--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-13 09:22:46</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,12 +756,6 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-13 09:22:46</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -662,7 +662,11 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-13 09:35:48</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -662,11 +662,6 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-13 09:35:48</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -754,6 +749,11 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>NSE:KALYANKJIL26AUG605CE</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-13 09:37:59</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,6 +756,101 @@
           <t>2026-08-13 09:37:59</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-13 09:41:26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1186.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="K4" t="n">
+        <v>25.24</v>
+      </c>
+      <c r="L4" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2475</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="U4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:DRREDDY26AUG1190PE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -845,12 +845,11 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:12:17</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -845,6 +845,16 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-08-13 11:16:22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-13 10:12:17</t>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,6 +860,101 @@
           <t>2026-08-13 10:12:17</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:03:59</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H5" t="n">
+        <v>605</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="K5" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="L5" t="n">
+        <v>35.14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2105</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="S5" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>58.03</v>
+      </c>
+      <c r="U5" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG605CE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -949,12 +949,16 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:17:29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,6 +959,101 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:31:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1236</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="K6" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="L6" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="M6" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1683</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="S6" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>63.14</v>
+      </c>
+      <c r="U6" t="n">
+        <v>37</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Realty</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:LODHA26AUG1240CE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1048,12 +1048,11 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:38:46</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1048,11 +1048,7 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-13 12:38:46</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,7 +1048,101 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:43:48</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="H7" t="n">
+        <v>107</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="N7" t="n">
+        <v>15822</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="S7" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>45.26</v>
+      </c>
+      <c r="U7" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:VMM26AUG107.5PE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1137,12 +1137,11 @@
           <t>NSE:VMM26AUG107.5PE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:48:42</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1048,6 +1048,11 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-13 13:06:31</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1048,11 +1048,7 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-13 13:06:31</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,7 +1048,6 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1143,6 +1142,101 @@
           <t>2026-08-13 12:48:42</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:14:29</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>106.26</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="H8" t="n">
+        <v>107</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15822</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="S8" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="U8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:VMM26AUG107.5PE</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1231,12 +1231,11 @@
           <t>NSE:VMM26AUG107.5PE</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:16:40</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,6 +1236,101 @@
           <t>2026-08-13 14:16:40</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:23:06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>14050</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>380</v>
+      </c>
+      <c r="J9" t="n">
+        <v>262.27</v>
+      </c>
+      <c r="K9" t="n">
+        <v>485.12</v>
+      </c>
+      <c r="L9" t="n">
+        <v>548.1799999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>632.28</v>
+      </c>
+      <c r="N9" t="n">
+        <v>131</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="S9" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="U9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:DIXON26AUG14000CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1325,12 +1325,11 @@
           <t>NSE:DIXON26AUG14000CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:27:35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1325,11 +1325,7 @@
           <t>NSE:DIXON26AUG14000CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-13 14:27:35</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1325,7 +1325,11 @@
           <t>NSE:DIXON26AUG14000CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:33:54</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -662,6 +662,16 @@
           <t>NSE:DRREDDY26AUG1190PE</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2026-08-13 11:13:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,6 +759,16 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>NSE:KALYANKJIL26AUG605CE</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-13 12:14:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
+++ b/backend/signal_logs/2026-08-13/signals_2026-08-13.xlsx
@@ -1068,6 +1068,11 @@
           <t>NSE:LODHA26AUG1240CE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Closed down ~27.75 (-6.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1157,6 +1162,11 @@
           <t>NSE:VMM26AUG107.5PE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed flat ~3.16 (+0.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-13 12:48:42</t>
@@ -1251,6 +1261,11 @@
           <t>NSE:VMM26AUG107.5PE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed down ~2.96 (-6.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-13 14:16:40</t>
@@ -1343,6 +1358,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:DIXON26AUG14000CE</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~360.05 (-5.2% from entry)</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
